--- a/api/clv1/codelist/Language.xlsx
+++ b/api/clv1/codelist/Language.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="550" uniqueCount="369">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="559" uniqueCount="375">
   <si>
     <t>code</t>
   </si>
@@ -208,6 +208,12 @@
     <t>Czech</t>
   </si>
   <si>
+    <t>cu</t>
+  </si>
+  <si>
+    <t>Church Slavic; Old Slavonic; Church Slavonic; Old Bulgarian; Old Church Slavonic</t>
+  </si>
+  <si>
     <t>cv</t>
   </si>
   <si>
@@ -253,7 +259,7 @@
     <t>el</t>
   </si>
   <si>
-    <t>Greek</t>
+    <t>Greek, Modern (1453-)</t>
   </si>
   <si>
     <t>English</t>
@@ -415,12 +421,24 @@
     <t>Herero</t>
   </si>
   <si>
+    <t>ia</t>
+  </si>
+  <si>
+    <t>Interlingua (International Auxiliary Language Association)</t>
+  </si>
+  <si>
     <t>id</t>
   </si>
   <si>
     <t>Indonesian</t>
   </si>
   <si>
+    <t>ie</t>
+  </si>
+  <si>
+    <t>Interlingue; Occidental</t>
+  </si>
+  <si>
     <t>ig</t>
   </si>
   <si>
@@ -748,7 +766,7 @@
     <t>oc</t>
   </si>
   <si>
-    <t>Occitan (post 1500)</t>
+    <t>Occitan (post 1500); Provençal</t>
   </si>
   <si>
     <t>oj</t>
@@ -1452,7 +1470,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G182"/>
+  <dimension ref="A1:G185"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -1876,10 +1894,10 @@
     </row>
     <row r="38" spans="1:4">
       <c r="A38" t="s">
-        <v>9</v>
+        <v>80</v>
       </c>
       <c r="B38" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D38" t="s">
         <v>9</v>
@@ -1887,7 +1905,7 @@
     </row>
     <row r="39" spans="1:4">
       <c r="A39" t="s">
-        <v>81</v>
+        <v>9</v>
       </c>
       <c r="B39" t="s">
         <v>82</v>
@@ -3466,6 +3484,39 @@
         <v>368</v>
       </c>
       <c r="D182" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="183" spans="1:4">
+      <c r="A183" t="s">
+        <v>369</v>
+      </c>
+      <c r="B183" t="s">
+        <v>370</v>
+      </c>
+      <c r="D183" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="184" spans="1:4">
+      <c r="A184" t="s">
+        <v>371</v>
+      </c>
+      <c r="B184" t="s">
+        <v>372</v>
+      </c>
+      <c r="D184" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="185" spans="1:4">
+      <c r="A185" t="s">
+        <v>373</v>
+      </c>
+      <c r="B185" t="s">
+        <v>374</v>
+      </c>
+      <c r="D185" t="s">
         <v>9</v>
       </c>
     </row>
